--- a/docs/features/047-advisory-findings-dispatch/testing-plan.xlsx
+++ b/docs/features/047-advisory-findings-dispatch/testing-plan.xlsx
@@ -671,7 +671,6 @@
           <t>The behaviour this replaces: runGovern returned above recordComplaint and runFix on a MERGE</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -699,8 +698,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -733,7 +730,6 @@
           <t>The invariant that matters most - a should finding never starts blocking</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -766,7 +762,6 @@
           <t>Spending an attempt on something no agent can fix changes nothing</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -794,8 +789,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -828,7 +821,6 @@
           <t>Dispatching would overrule the one explicit instruction the repo gave about that gate</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -861,7 +853,6 @@
           <t>FIX empties advisoryFindings and the merge path is the only thing that posts it, so a split would report the gate nowhere</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -889,8 +880,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -918,8 +907,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -947,8 +934,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -976,8 +961,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1005,8 +988,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1034,8 +1015,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1068,7 +1047,6 @@
           <t>The existing suite therefore validates that the new default breaks nothing</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1101,7 +1079,6 @@
           <t>It went red against the first implementation, which is how the distinction was found</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1129,8 +1106,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1150,7 +1125,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PENDING - ql-desktop #103 reopened after this merges is the intended check</t>
+          <t>STILL PENDING 2026-09-22, and the original plan for it was wrong. ql-desktop #103 merged rather than being reopened, and its findings could never have closed this row anyway. OBSERVED LIVE: four governed pull requests since this merged - ql-desktop #105, #106, #107 and #109 - each reported advisory findings and merged. Every one of them was `task#provenance`, which is built autoFixable:false (src/verdict/task-provenance.ts:160), so the new guard DECLINED and fell back to MERGE. That is correct behaviour and it exercises the decline branch live, but it is not this row. The dispatch branch needs an advisory finding the REVIEW judged minor, which is auto-fixable - not a task-provenance notice and not a gate finding.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1160,10 +1135,9 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gate 3</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Gate 3. Cannot be forced: it needs a review to volunteer an auto-fixable `should`. As of 2026-09-22 GitHub Actions is refusing to start jobs on this account for billing, so no governance run of any kind can be observed until that clears.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G300"/>
